--- a/extenbooks/XS1404.xlsx
+++ b/extenbooks/XS1404.xlsx
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1355,121 +1355,130 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XS1404 = S506 / XS1401: the ratio of the ST exploitation rate to the Mohun (2005 SM method) exploitation rate. This is a derived series, not directly reported by Mohun. It quantifies the systematic understatement in ST's exploitation rate arising from ST's inferior approximation procedures. The mean ratio ≈ 1.61 means that the Mohun SM exploitation rate is on average about 61% higher than the ST exploitation rate over 1964-2001.</t>
+          <t>STUDY ANCHOR + ORIENTATION RESOLUTION (Mohun 2005 Figure 4). Mohun publishes: ST e avg 1964-82 = 1.71, 2001 = 2.22; SM e avg 1964-82 = 1.97, 2001 = 3.00. The Mohun-published ST/SM ratio is therefore 1.71/1.97 = 0.868 (1964-82) and 2.22/3.00 = 0.74 (2001) — i.e. BELOW 1 (ST below SM). XS1404 = S506/XS1401 = e_ST_book / e_mohun_reconstruction, computed mean = 1.163 over 1948-1989 (min 1.020, max 1.304) — ABOVE 1, the INVERSE orientation, because the XS1401 reconstruction yields a LOWER exploitation rate than the ST book rate (opposite to Mohun published finding that SM&gt;ST). The registry claimed derived mean = 1.61 matches NEITHER the computed series (1.163) NOR Mohun published ST/SM (0.74-0.87) NOR SM/ST (1.15-1.35); it is unsourced and is REMOVED. No external scalar anchor exists for the 1948-1989 ratio; the year refvals are the series own output (tautological). Honest reference = the construction identity XS1404-A == S506-A / XS1401-A (holds exactly, max abs err 2.2e-16).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Series registry XS1404; Mohun_2005, Fig 4; full_transcription.md Section 4</t>
+          <t>Mohun 2005, Figure 4 (Rate of surplus value), CJE 29(5):799-815 (Section 4, ~p.812)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>classification_explanation</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The ST/Mohun ratio of 1.61 reflects two separable effects: (1) Approximation method differences — Mohun's SM procedures yield lower variable capital estimates than ST's, hence higher exploitation rates (this is the 2005 paper's contribution). (2) Classification boundary differences — Mohun's 2013 paper adds supervisory/managerial workers to unproductive labor explicitly, treating 'supervision' as a distinct unproductive category. In ST, managers are partially absorbed into the production worker count; in Mohun 2013 they are systematically excluded. The ST/Mohun ratio captures the combined effect of both.</t>
+          <t>XS1404 = S506 / XS1401: the ratio of the ST exploitation rate to the Mohun (2005 SM method) exploitation rate. This is a derived series, not directly reported by Mohun. It quantifies the systematic understatement in ST's exploitation rate arising from ST's inferior approximation procedures. The mean ratio ≈ 1.61 means that the Mohun SM exploitation rate is on average about 61% higher than the ST exploitation rate over 1964-2001.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2005, Introduction; Mohun_2013, Section 2.1; full_transcriptions</t>
+          <t>Series registry XS1404; Mohun_2005, Fig 4; full_transcription.md Section 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>benchmark_comparison</t>
+          <t>classification_explanation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Figure 4 of Mohun (2005) shows: ST exploitation rate average 1964-1982 = 1.71, 2001 = 2.22. SM exploitation rate average 1964-1982 = 1.97, 2001 = 3.00. If ST e ≈ 2.22 and SM e ≈ 3.00 in 2001, the ST/Mohun ratio in 2001 = 2.22/3.00 = 0.74. The ST/Mohun ratio is thus the INVERSE of the ratio described above — ST reports LOWER rates than SM. The series registry entry records mean = 1.61, which therefore represents SM/ST (Mohun rate divided by ST rate, i.e., XS1404 = S506/XS1401 where S506 is ST and XS1401 is Mohun, and Mohun &gt; ST). Check: 3.00/2.22 = 1.35 for 2001 alone; the mean 1.61 is over the full 1964-2001 period where the ratio varies.</t>
+          <t>The ST/Mohun ratio of 1.61 reflects two separable effects: (1) Approximation method differences — Mohun's SM procedures yield lower variable capital estimates than ST's, hence higher exploitation rates (this is the 2005 paper's contribution). (2) Classification boundary differences — Mohun's 2013 paper adds supervisory/managerial workers to unproductive labor explicitly, treating 'supervision' as a distinct unproductive category. In ST, managers are partially absorbed into the production worker count; in Mohun 2013 they are systematically excluded. The ST/Mohun ratio captures the combined effect of both.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2005, Fig 4; Series registry XS1404 construction formula S506/XS1401</t>
+          <t>Mohun_2005, Introduction; Mohun_2013, Section 2.1; full_transcriptions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>benchmark_comparison</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Series registry specifies construction: step 1 op=derive, formula='S506 / XS1401', inputs=['S506', 'XS1401'], output='XS1404-COMBINED'. Reference value: mean = 1.61. Expected range [1.0, 2.5]. If the formula is S506/XS1401 and the reference mean is 1.61, then S506 (ST) &gt; XS1401 (Mohun), suggesting the Mohun 2005 series XS1401 captures the exploitation rate with ST's approximation procedures but Mohun's boundary. Alternatively the ratio is ST benchmark/SM = lower number. The mean 1.61 should be interpreted as the average cross-validation factor between the two classification systems over 1964-2001.</t>
+          <t>Figure 4 of Mohun (2005) shows: ST exploitation rate average 1964-1982 = 1.71, 2001 = 2.22. SM exploitation rate average 1964-1982 = 1.97, 2001 = 3.00. If ST e ≈ 2.22 and SM e ≈ 3.00 in 2001, the ST/Mohun ratio in 2001 = 2.22/3.00 = 0.74. The ST/Mohun ratio is thus the INVERSE of the ratio described above — ST reports LOWER rates than SM. The series registry entry records mean = 1.61, which therefore represents SM/ST (Mohun rate divided by ST rate, i.e., XS1404 = S506/XS1401 where S506 is ST and XS1401 is Mohun, and Mohun &gt; ST). Check: 3.00/2.22 = 1.35 for 2001 alone; the mean 1.61 is over the full 1964-2001 period where the ratio varies.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Series registry XS1404; Mohun_2005</t>
+          <t>Mohun_2005, Fig 4; Series registry XS1404 construction formula S506/XS1401</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>construction_note</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Series registry specifies construction: step 1 op=derive, formula='S506 / XS1401', inputs=['S506', 'XS1401'], output='XS1404-COMBINED'. Reference value: mean = 1.61. Expected range [1.0, 2.5]. If the formula is S506/XS1401 and the reference mean is 1.61, then S506 (ST) &gt; XS1401 (Mohun), suggesting the Mohun 2005 series XS1401 captures the exploitation rate with ST's approximation procedures but Mohun's boundary. Alternatively the ratio is ST benchmark/SM = lower number. The mean 1.61 should be interpreted as the average cross-validation factor between the two classification systems over 1964-2001.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Series registry XS1404; Mohun_2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>supervisory_labor_link</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>The key methodological difference driving the classification gap: Mohun (2013) explicitly separates 'supervisory and managerial labor' as unproductive, following Moseley (1991). This category ('managers-plus-capitalists') constitutes 18.7% of total employment on average 1964-2010. In ST (1994), the BLS production worker criterion partially excludes supervisors in Manufacturing, Mining, and Construction, but in private service-producing industries the nonsupervisory definition includes lower-level supervisors. Mohun's more systematic exclusion of all supervisory labor expands the unproductive sector boundary, reduces measured productive labor, and increases the measured exploitation rate relative to ST.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Mohun_2013, Section 3; full_transcription.md</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Derived ratio S506/XS1401 (ST rate / Mohun 2005 SM rate). Mean ≈ 1.61 over 1964-2001. Reflects combined effect of: (1) ST approximation procedure errors (services wage overestimate, transportation wage overestimate); (2) classification boundary differences (Mohun's systematic exclusion of supervisory labor). The ratio rises over time as the post-1980 exploitation rate increase is larger under SM than under ST.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ratio interpretation depends on whether S506 or XS1401 is the numerator — registry formula S506/XS1401 with mean=1.61 should be verified against actual computed values</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1486,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Two distinct sources of divergence (approximation errors vs. classification boundaries) are conflated in a single ratio</t>
+          <t>Ratio interpretation depends on whether S506 or XS1401 is the numerator — registry formula S506/XS1401 with mean=1.61 should be verified against actual computed values</t>
         </is>
       </c>
     </row>
@@ -1485,23 +1494,23 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Two distinct sources of divergence (approximation errors vs. classification boundaries) are conflated in a single ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Period mismatch: XS1401 covers 1964-2001; S506 covers different period — ratio only defined over intersection</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1518,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XS1402</t>
+          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1526,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XS1403</t>
+          <t>XS1402</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1534,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S506</t>
+          <t>XS1403</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1542,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XS1501</t>
+          <t>S506</t>
         </is>
       </c>
     </row>
@@ -1541,49 +1550,57 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
+          <t>XS1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>XS1502</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mohun_2013</t>
+          <t>Mohun_2005</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Mohun_2013</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1606,7 +1623,7 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1653,7 +1670,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1404-COMBINED</t>
+          <t>XS1404-A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1764,7 +1781,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"mean": 1.61}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1404.xlsx
+++ b/extenbooks/XS1404.xlsx
@@ -1098,7 +1098,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/(derived from S506 and XS1401)` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1404_st_mohun_ratio.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1404_st_mohun_ratio.py`.</t>
+          <t>`data/source/external_studies/(derived from S506 and XS1401)` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1404_st_mohun_ratio.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1404_st_mohun_ratio.py`.</t>
         </is>
       </c>
     </row>
